--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>70721a5ff8256637b6b5f57d365e114015f3725b53ca9ad18fffa69a39c91ec6</t>
+          <t>53db7e2cee9320b8379f52894757df6ba9f612ab885c0d5c0f52496dc64b8ac2</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>c06acd04c8b53d561ca2a5800f4b22d1f7a2c9db267cdf07cfe158db3a0308ad</t>
+          <t>0f0cbb545b09706dc8c3bca13d6615f8098ba51c73a7d450fbb06b0666e4346b</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>4216771030f2c054403525691f7ae162dcfe628fa02eb8b47ea79d558542c7f5</t>
+          <t>e1ab22bfe59ff0b38a83de0da9717104c6913157788cef3479b119c88f6a9e2e</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>49ecab0683c89d7ea49c4e43c0cedefd320c4a7349e7d3d9c9dc5d7eab6add61</t>
+          <t>6732bb8b396089a0429e9763c01b4e9e14aa0beb67fb0023aaab3b41b095fab1</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>82e7538c95fbf72d95a922bb04b96838a65c864e04009be66d0cd1c270d8a49a</t>
+          <t>48a6535725e7c8b27a1eb9808a55c98a174ccfff33ddb1f87e3b192508f9e8c9</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>44d163a63139eac91a6de0752f3eb93f9748552363eae845cea577c1ad88416d</t>
+          <t>956217c67e6f17d593175b8491bfeb0394242723d25f1f81495c102c5a5456e5</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>0f59da56446b1482e591ebd8b8b41c84f339d01de672db61029621f3b6d0959c</t>
+          <t>3d9070f728890a0ea9b9e8df1667e72c40126ac616887e6c23ca416e9574b0ec</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>6e08f463a03686bd2375a3675e9be5036fb70b49315b13607ca498af4c02a83c</t>
+          <t>92547e515c9ee5702bdb6cd86b2fac4bac44b5beaa4820856e4ee9939456d381</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>4060db2901d2dc7ef0f48dea23c1681d827643cb800c2ad5045361ba48e196a5</t>
+          <t>e29875a50e34747cc00a941443a74dfa7d51a05595050ea3e373f7fba25e7dfa</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>8cb8a5f993b247b21b2c35ead9845607dde9684b98625f6439d34c2ad8b260f7</t>
+          <t>cd404b49ef6bc71baae54e1938a19ecd53df86f26eafd324c31647c2d4908c6d</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>2f002d9f3a23d32e396b0abd164c4b5d4bb09f61157290576587569afbec90b3</t>
+          <t>f41b01e958ea25d102c2fdf546586a161afb1eb3ecd57255758781764048adbc</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>01330343c347c55db3f3248e45318eb73b3c906a595b89100a9778ac0ee3407f</t>
+          <t>a77f72bdfcddecc13489ab909ea9e41c508c159ba44e5c4e982ae61f9bd55ff4</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>f7cec3510ae62f3add2a32de0d6df23b3f6f670f3215ab80531f19d4eaa7affb</t>
+          <t>e04512342d23866288ae832023df3393dd8679b7058259397b507a4bd832ddcf</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>5165375a65a8dddbebe816eb759e2ac85e8c57c3d839cba90301a6fa099ad256</t>
+          <t>3c5e4dcaafedea7afd8613d3acd4edd43d24ed6bfa912c282885a3ab3e423968</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>d44c9a412706d369f81aac91e8fe83959fd1826dec1e18038f14289404714eec</t>
+          <t>03d3304d280f995ab4c030c97736c1fa8496741bbd1b5c5a9bcb9f1c5debf4f4</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>0704b8a4fe1e2971ad48c597b10bd127440dab6e45b7a65704ec72dec2f797c2</t>
+          <t>0c72f92e1ed6301f8b640b57dd62deeba60cdf04e4c4f46cbb04d9bd56da3dff</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>25be2bc34dd75fa12367641a74c1940640835b40b9b6704bde3ee3c68e569446</t>
+          <t>247d397a215aaa6c5007e6d177836278904ed357e60dc821939ac4d42a24f558</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>ab743223c96931171d38dd49bcd501fdff9d71c0f4a4452a17becc4f91214f73</t>
+          <t>d755edb869eb8b7c42324eb63e989ac80d0c945551774659945eaaeec2c3c538</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>01d9bb7f97fdbf274b14fe93d1b0c59309af0f3065bf6b9aacad41780a31e0e7</t>
+          <t>3e74748e263085ea851ff90a5ed0ac6d5a57a7152eaa8a68116f0b8a123c5e63</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>53db7e2cee9320b8379f52894757df6ba9f612ab885c0d5c0f52496dc64b8ac2</t>
+          <t>ed93bbbe5e783db58ee68cc7c6bd1b67c8bddfda6e4bcf4f117caa3eb958ad36</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>0f0cbb545b09706dc8c3bca13d6615f8098ba51c73a7d450fbb06b0666e4346b</t>
+          <t>7af23e625fe5532bc477d24090f569e36b0c7fd08fcabca86223a5bfc2fdf93d</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>e1ab22bfe59ff0b38a83de0da9717104c6913157788cef3479b119c88f6a9e2e</t>
+          <t>3db8b7738e6fdfb499f4bcafe6f65511b9d7f353a25b76287a3d0d8271226635</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>6732bb8b396089a0429e9763c01b4e9e14aa0beb67fb0023aaab3b41b095fab1</t>
+          <t>630cf97dd6c0fa67d811442c0331d3d3da121c6740b3b9c89953f16a5df1323d</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>48a6535725e7c8b27a1eb9808a55c98a174ccfff33ddb1f87e3b192508f9e8c9</t>
+          <t>da981b0443bc402067ccc6d3f6c8fdc404093a0e48dfd1a8d4a609c941c27514</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>956217c67e6f17d593175b8491bfeb0394242723d25f1f81495c102c5a5456e5</t>
+          <t>48bd29fec89d6825df5001c7f0cf3bbf3246d354c2854a94a870d44c4ec9af5d</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>3d9070f728890a0ea9b9e8df1667e72c40126ac616887e6c23ca416e9574b0ec</t>
+          <t>d182a3fe80a93adc1e571d2148db76bf0313fd21984ab5e1bdeb1533b9d408c2</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -3202,14 +3202,14 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>15</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>92547e515c9ee5702bdb6cd86b2fac4bac44b5beaa4820856e4ee9939456d381</t>
+          <t>630344b919911dc7ae5159e3b980700debed1d18d9d683eedf4a1ef6aaa23494</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>e29875a50e34747cc00a941443a74dfa7d51a05595050ea3e373f7fba25e7dfa</t>
+          <t>f6e7e8db679effecf6cbdcc06bd3c1f948c450b32916ada63fc018bba179ee0c</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>cd404b49ef6bc71baae54e1938a19ecd53df86f26eafd324c31647c2d4908c6d</t>
+          <t>0281b6cb7c6d8f146f17520ca4d322e64e396e47f5eb91ae2de178acf3f203cf</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>f41b01e958ea25d102c2fdf546586a161afb1eb3ecd57255758781764048adbc</t>
+          <t>e7b62472fdeede976001eaf06339e0ab042a24fe8dd45c2d2c410daaa5eef8ba</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>a77f72bdfcddecc13489ab909ea9e41c508c159ba44e5c4e982ae61f9bd55ff4</t>
+          <t>6dc2f2dfc67a26e29340dbbaf3643a61880376e991a1e75b0e0088046ef84b12</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>e04512342d23866288ae832023df3393dd8679b7058259397b507a4bd832ddcf</t>
+          <t>32598185ca1e8841f98e04332915af72837a5088347e8414d95a8281e21af998</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>3c5e4dcaafedea7afd8613d3acd4edd43d24ed6bfa912c282885a3ab3e423968</t>
+          <t>1aa4f61c30aca1289e879ba07aeb28a27dafcdc47ae6b9ab41fc63eadfaac1d6</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>03d3304d280f995ab4c030c97736c1fa8496741bbd1b5c5a9bcb9f1c5debf4f4</t>
+          <t>91727b52e34a8357f35f68a313e933b98e69f9dc754544affd21b748e5f4e85f</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>0c72f92e1ed6301f8b640b57dd62deeba60cdf04e4c4f46cbb04d9bd56da3dff</t>
+          <t>8c16ca8e9e3291a3ae6a6064626cf1728bd21ba7268b52154b5ab771af79c1e4</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>247d397a215aaa6c5007e6d177836278904ed357e60dc821939ac4d42a24f558</t>
+          <t>eee858daa988e56835532ee92513107db9e2c052fcdce79c8dcefb70376ae18b</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>d755edb869eb8b7c42324eb63e989ac80d0c945551774659945eaaeec2c3c538</t>
+          <t>53ba8e8a2afdd128cd8aa900f74ecffac44f1e3955f9db04b394cc4d721ca7cf</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>3e74748e263085ea851ff90a5ed0ac6d5a57a7152eaa8a68116f0b8a123c5e63</t>
+          <t>c94836cd530ec1c930cb7a3366f29fa3c093f0df1421f2b739755b385b02d288</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>ed93bbbe5e783db58ee68cc7c6bd1b67c8bddfda6e4bcf4f117caa3eb958ad36</t>
+          <t>76583d019548146238b18bb5f0618ba3e20017e89b57a7decd9e675573c6c8de</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>7af23e625fe5532bc477d24090f569e36b0c7fd08fcabca86223a5bfc2fdf93d</t>
+          <t>7bb7f04d08c3e2a2829f673b71b9740b07cf2a1b6509111d91c2080ee5c5064b</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>3db8b7738e6fdfb499f4bcafe6f65511b9d7f353a25b76287a3d0d8271226635</t>
+          <t>88c79c0822f3926e3d5ac7d1d8e6caa24ebf5de7b7702192bc2b46bbfdb76bb7</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>630cf97dd6c0fa67d811442c0331d3d3da121c6740b3b9c89953f16a5df1323d</t>
+          <t>c6c333782414f1cdc0d8e51c3e8ce970dbbe18fe6ef6e47490531f6297cf4537</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>da981b0443bc402067ccc6d3f6c8fdc404093a0e48dfd1a8d4a609c941c27514</t>
+          <t>edb43f9e32a80e615d17b187574a731aedadf1cc41308492e83f7188d6f785c0</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>48bd29fec89d6825df5001c7f0cf3bbf3246d354c2854a94a870d44c4ec9af5d</t>
+          <t>20deb904c1cfc58b9e87c8b81bd1cf8f26524726e757249b4c6a1d1f083a7fd6</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>d182a3fe80a93adc1e571d2148db76bf0313fd21984ab5e1bdeb1533b9d408c2</t>
+          <t>4727c9a0937c54b50242c8927e5e3222cc2b988117ef9533ad4dd8d4d8149bc9</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -3202,14 +3202,14 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>15</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>630344b919911dc7ae5159e3b980700debed1d18d9d683eedf4a1ef6aaa23494</t>
+          <t>229aba6930394ace7486f220f470c1c6a12440dac5b5642c5e229c1dbf3343dd</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>f6e7e8db679effecf6cbdcc06bd3c1f948c450b32916ada63fc018bba179ee0c</t>
+          <t>00433fe89c5d446ea01c2a19f069f7a20bbc44e565f3c592ef782fd7274ea68f</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>0281b6cb7c6d8f146f17520ca4d322e64e396e47f5eb91ae2de178acf3f203cf</t>
+          <t>3be06c357185b6a5293ab77379b8034c63e2501e58fed35fc026891bd4a6a291</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>e7b62472fdeede976001eaf06339e0ab042a24fe8dd45c2d2c410daaa5eef8ba</t>
+          <t>43b5003fc43e0b7526cd65501f301cd099980f9f0c8bcb1a2de954577db9f4d4</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>6dc2f2dfc67a26e29340dbbaf3643a61880376e991a1e75b0e0088046ef84b12</t>
+          <t>7acf8db892da674ac9478408ce8f55ea6335882f2f7d08d44d2757a2597761a1</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>32598185ca1e8841f98e04332915af72837a5088347e8414d95a8281e21af998</t>
+          <t>5668ef26abc52f6ccc3d69db8c1cbc41a6c21ec6dbd0417d5ac54244109b7754</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>1aa4f61c30aca1289e879ba07aeb28a27dafcdc47ae6b9ab41fc63eadfaac1d6</t>
+          <t>037015d69e9d63ff13f3cccb7fb2adbf4e1fac24eeabdc92a9195a4c16083f7c</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>91727b52e34a8357f35f68a313e933b98e69f9dc754544affd21b748e5f4e85f</t>
+          <t>b2a12fdf9b7aacda65eb24b2854b0ca4e2636d18c6cf61211f7cdfa0479ad949</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>8c16ca8e9e3291a3ae6a6064626cf1728bd21ba7268b52154b5ab771af79c1e4</t>
+          <t>8aaba76487fe3be0a2dd4ffbf627dbf694f2a935a5ec23cc333d008e7cac2138</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>eee858daa988e56835532ee92513107db9e2c052fcdce79c8dcefb70376ae18b</t>
+          <t>9bcc1f0c292bdf9d648a320815fb3fc4f51e2dccb998eb5fe425b1c75fd37720</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>53ba8e8a2afdd128cd8aa900f74ecffac44f1e3955f9db04b394cc4d721ca7cf</t>
+          <t>00195c6bbc90d27ee98686ea28fedb7528b0042b443088c8c1fd29b2eb569709</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>c94836cd530ec1c930cb7a3366f29fa3c093f0df1421f2b739755b385b02d288</t>
+          <t>66479f47bc851ef114a918a6ed5dc10813a207703973c5207d10999c6a2e2171</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>76583d019548146238b18bb5f0618ba3e20017e89b57a7decd9e675573c6c8de</t>
+          <t>175738022b175f6484f61597312f6bc9a2e2cd9d15c462224547dc0914ba391e</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>88c79c0822f3926e3d5ac7d1d8e6caa24ebf5de7b7702192bc2b46bbfdb76bb7</t>
+          <t>47edd7b9ba9495e6cdeffaa267e9e98f21cab2935be3a4339899de4016c9bdae</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>c6c333782414f1cdc0d8e51c3e8ce970dbbe18fe6ef6e47490531f6297cf4537</t>
+          <t>12e13220c013db373166a64d0e1b79eb2b173ef87085d1bb1ed0158365999fbc</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>20deb904c1cfc58b9e87c8b81bd1cf8f26524726e757249b4c6a1d1f083a7fd6</t>
+          <t>f5dddbd2547f6fca60e6d3f9d71efe8786af50fe2eb0fc5f748384f43521f267</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>229aba6930394ace7486f220f470c1c6a12440dac5b5642c5e229c1dbf3343dd</t>
+          <t>5aeb3dfdee22e3920746e2783bf7ac8769a4db2855ed421cfd1ecdc8157bd122</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>3be06c357185b6a5293ab77379b8034c63e2501e58fed35fc026891bd4a6a291</t>
+          <t>0b15df11a90ae7b789721bd6f68de28398f82e63d8f15a16ff2a861134df51fb</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>b2a12fdf9b7aacda65eb24b2854b0ca4e2636d18c6cf61211f7cdfa0479ad949</t>
+          <t>cde64a1a2c25b9d66e0ff986686f6ebe4723dc44b70deb3ac27d47748eb99d90</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>8aaba76487fe3be0a2dd4ffbf627dbf694f2a935a5ec23cc333d008e7cac2138</t>
+          <t>6c02e1f7e9f7ff86c44a667cf3453e847d5a2b88cef215a0ebcee1765b796b49</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>9bcc1f0c292bdf9d648a320815fb3fc4f51e2dccb998eb5fe425b1c75fd37720</t>
+          <t>ab3ddc795519e2251ed328cee2b54b7777eea5b48b963a8ad1e3d2764ed9510e</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>00195c6bbc90d27ee98686ea28fedb7528b0042b443088c8c1fd29b2eb569709</t>
+          <t>b58bab2e9ec1a2d1a640730405d4acee442dcb5d90fe15833a5038cb505da991</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>175738022b175f6484f61597312f6bc9a2e2cd9d15c462224547dc0914ba391e</t>
+          <t>fad4cdcad262f4d988becdca48b60d91c109fdeba9e1033ad02d27edba92d38c</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>47edd7b9ba9495e6cdeffaa267e9e98f21cab2935be3a4339899de4016c9bdae</t>
+          <t>59cbc414b845025977d45711a3b2d169e389b0a917fad328e95ca467fae9d4e1</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>12e13220c013db373166a64d0e1b79eb2b173ef87085d1bb1ed0158365999fbc</t>
+          <t>29f725b5c91d725e28593c7908de0efd9732c2281ed764868f456837219f08e4</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>f5dddbd2547f6fca60e6d3f9d71efe8786af50fe2eb0fc5f748384f43521f267</t>
+          <t>fe065fcecb1f69bb81683cd9d536387ec8258c03827f54fa7b3727e8d300801a</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>0b15df11a90ae7b789721bd6f68de28398f82e63d8f15a16ff2a861134df51fb</t>
+          <t>dd76409fe3017516b49d1282e735b40a5c145c015b9b50cc04a3c09505265e91</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>cde64a1a2c25b9d66e0ff986686f6ebe4723dc44b70deb3ac27d47748eb99d90</t>
+          <t>9b6da1ef30540403b3f55d8ad9dcc2c96d2f286af876d2f8b1da53d5e0aacf4d</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>6c02e1f7e9f7ff86c44a667cf3453e847d5a2b88cef215a0ebcee1765b796b49</t>
+          <t>d736b44b80ea464108cb71935bedc4a2745820432aab73d18ecb9d06b7e77cd2</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>ab3ddc795519e2251ed328cee2b54b7777eea5b48b963a8ad1e3d2764ed9510e</t>
+          <t>7a62580be557d2dd328282092cce8578f23e1851aa0477107abb9c9558bfb7bf</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>b58bab2e9ec1a2d1a640730405d4acee442dcb5d90fe15833a5038cb505da991</t>
+          <t>3b2acf51794611dcf328087cfce9a3b331f670d3b151fade4375973e66336e30</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>fad4cdcad262f4d988becdca48b60d91c109fdeba9e1033ad02d27edba92d38c</t>
+          <t>bbac0fc81623e0d86935a409df73815e00ff8d3097c5224b4dc794fcc2106792</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>59cbc414b845025977d45711a3b2d169e389b0a917fad328e95ca467fae9d4e1</t>
+          <t>c6cdebb67090a0053d1d4d0a34c0e1d176c3ea0bccd0625100298299a6e764cc</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>29f725b5c91d725e28593c7908de0efd9732c2281ed764868f456837219f08e4</t>
+          <t>816b236ee89ca5b95215829682b4788802aaa6b4a803232cdfccf9791b6028f1</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>fe065fcecb1f69bb81683cd9d536387ec8258c03827f54fa7b3727e8d300801a</t>
+          <t>49c1750e93ef497ea971f0e1870c476b9b62f0b56260c85424f096c6a6629a1e</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>5aeb3dfdee22e3920746e2783bf7ac8769a4db2855ed421cfd1ecdc8157bd122</t>
+          <t>a85aa0143dcf05c501ab2382f86f8561db920d1ded614e307070f66232df5bf9</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>dd76409fe3017516b49d1282e735b40a5c145c015b9b50cc04a3c09505265e91</t>
+          <t>8cfb06a3c10fe352b721f6264607d11d83b5452e8b02ea275f64a65e6a3b65f2</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>9b6da1ef30540403b3f55d8ad9dcc2c96d2f286af876d2f8b1da53d5e0aacf4d</t>
+          <t>77b13e468a525dac2856396244830dab4b7ed436d98b5a8e7500779eb1370b66</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>d736b44b80ea464108cb71935bedc4a2745820432aab73d18ecb9d06b7e77cd2</t>
+          <t>10e6270f46fac40ed0173605315f882ddc6584cd555c67aefec20536c8c2e9a1</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>7a62580be557d2dd328282092cce8578f23e1851aa0477107abb9c9558bfb7bf</t>
+          <t>e55ee8240b8c27db63d22186d875253373f8444dac0fdaffe90f49dce43df481</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>3b2acf51794611dcf328087cfce9a3b331f670d3b151fade4375973e66336e30</t>
+          <t>cd1572bba7eebe627f608f8e6f1d56b8f60ad2bea01b944f6f62e6e2ad845ac9</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>bbac0fc81623e0d86935a409df73815e00ff8d3097c5224b4dc794fcc2106792</t>
+          <t>baf26ebe1f8e1fa36d343f93933e174e65992c77da973a8d41e3f9facfa1dbd4</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>c6cdebb67090a0053d1d4d0a34c0e1d176c3ea0bccd0625100298299a6e764cc</t>
+          <t>64ccd39a505f18b8797d95dd1d8177f5cdad083dd22ca4d2f4bc34a0f7fb8b17</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>816b236ee89ca5b95215829682b4788802aaa6b4a803232cdfccf9791b6028f1</t>
+          <t>d34412762f3f71cb269bbc5e37b4aca9738bdd15607d63056956864e035a5819</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>49c1750e93ef497ea971f0e1870c476b9b62f0b56260c85424f096c6a6629a1e</t>
+          <t>33443e77cc16dc7eec0533fcfb7e6156b77c4a033d52f94028b2f1be7ae6f219</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>a85aa0143dcf05c501ab2382f86f8561db920d1ded614e307070f66232df5bf9</t>
+          <t>8f435d7761321ae6c7267f8d5ae9a68dc034af9471c913d8993617aefba42170</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>8cfb06a3c10fe352b721f6264607d11d83b5452e8b02ea275f64a65e6a3b65f2</t>
+          <t>fb33c88d1bc1bd5cb4a884c126bdc887d0866b0e8bf37d34e8eecbbb0d848fc8</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>77b13e468a525dac2856396244830dab4b7ed436d98b5a8e7500779eb1370b66</t>
+          <t>ac1a7f51e8a37b2992b4d8ab6d278fe5279aee9a6875fe63f15654baab8bbd4c</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>10e6270f46fac40ed0173605315f882ddc6584cd555c67aefec20536c8c2e9a1</t>
+          <t>244fe77a80daa009da9279bf5a91123b951eed75ac1f5e2cddcb6e85d2b0fdf5</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>e55ee8240b8c27db63d22186d875253373f8444dac0fdaffe90f49dce43df481</t>
+          <t>3bcd2f29c52086eb14b43dccc980b372b92d76599d1ef3e4a98b15f261d013f1</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>cd1572bba7eebe627f608f8e6f1d56b8f60ad2bea01b944f6f62e6e2ad845ac9</t>
+          <t>d6865451f45dcd8b6f2d365c6d21816d8ef60c476cc2116806f3ceb8d6ee5e36</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>baf26ebe1f8e1fa36d343f93933e174e65992c77da973a8d41e3f9facfa1dbd4</t>
+          <t>728709b2f941ab31d78cbe1a37d24b321a255fd9b040286d209e88b7db6b6201</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>64ccd39a505f18b8797d95dd1d8177f5cdad083dd22ca4d2f4bc34a0f7fb8b17</t>
+          <t>25ca2afa2d28b46416ef6b6a686560dc73e7670eb309f89ee7fa26ea403ced4e</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>d34412762f3f71cb269bbc5e37b4aca9738bdd15607d63056956864e035a5819</t>
+          <t>d8d40325b61cfd19b7068ee11e93f873f21678255dce0385a15ea49cf3f34b53</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>33443e77cc16dc7eec0533fcfb7e6156b77c4a033d52f94028b2f1be7ae6f219</t>
+          <t>1f5ea70ae730ec609ca29c33738c438befdf80f536999f04acc193e9fa510a35</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>8f435d7761321ae6c7267f8d5ae9a68dc034af9471c913d8993617aefba42170</t>
+          <t>3e2a727247115523ab43062e65a3a0a0fd6095a107e9b3930275f54b1ea0d76e</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>fb33c88d1bc1bd5cb4a884c126bdc887d0866b0e8bf37d34e8eecbbb0d848fc8</t>
+          <t>8e7cf92207067038d24d371cf536872ee4d8c0ebf79d6d93e6b76b4567371fe0</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>ac1a7f51e8a37b2992b4d8ab6d278fe5279aee9a6875fe63f15654baab8bbd4c</t>
+          <t>4bbd4fc9364615ed1399043e0f6c5d9bd9769d9e131993b301a71893d585ee4d</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>244fe77a80daa009da9279bf5a91123b951eed75ac1f5e2cddcb6e85d2b0fdf5</t>
+          <t>a8a2d2b5ba93020d6ce662b96cadc06240e2e3829288680c5a2db7c28a35261e</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>3bcd2f29c52086eb14b43dccc980b372b92d76599d1ef3e4a98b15f261d013f1</t>
+          <t>0a3881aee8c28c6c6cbc66f7d3cb8549e6d90522f27f2e5304214f2c9ef588c3</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>d6865451f45dcd8b6f2d365c6d21816d8ef60c476cc2116806f3ceb8d6ee5e36</t>
+          <t>dba29de70f28d13ce03f42b353730c7a0841ab76d892c3002e7a2e457feec960</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>728709b2f941ab31d78cbe1a37d24b321a255fd9b040286d209e88b7db6b6201</t>
+          <t>5a90c4f2d8d4a94e7c60a04f3a1088899ef1e6160229d4e1a98e3ee9ed6f0a43</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>25ca2afa2d28b46416ef6b6a686560dc73e7670eb309f89ee7fa26ea403ced4e</t>
+          <t>f2559f4f2f86e25f77d3a9cded30a60c6bd5b4048461692ff382f09dd91e7dbf</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>d8d40325b61cfd19b7068ee11e93f873f21678255dce0385a15ea49cf3f34b53</t>
+          <t>11e4bf979f80415b420a73e1d52561fb9673e515a36225cf961b5625871d01ef</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>1f5ea70ae730ec609ca29c33738c438befdf80f536999f04acc193e9fa510a35</t>
+          <t>37eb740001d74dcab194d6a4168598d45e4ab84e77cd1dfe6a55a07f40782849</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>3e2a727247115523ab43062e65a3a0a0fd6095a107e9b3930275f54b1ea0d76e</t>
+          <t>e96d6e039e7802c651269e09452d2a0d5f92f2cebdecbf6054bd63111e92ab1c</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>8e7cf92207067038d24d371cf536872ee4d8c0ebf79d6d93e6b76b4567371fe0</t>
+          <t>975689cbc0a01c2e52ec3f88f5b90f182910c409af6f2504f4aa9f51e8d56a57</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>4bbd4fc9364615ed1399043e0f6c5d9bd9769d9e131993b301a71893d585ee4d</t>
+          <t>4393b098cdb1b5b6c5aca762172bd50798943f407b16565781cbf17c2e30c314</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>a8a2d2b5ba93020d6ce662b96cadc06240e2e3829288680c5a2db7c28a35261e</t>
+          <t>0ec893cace11b88af0679a97ebdd57e33e0387603c9267443655a6244024d0b2</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0a3881aee8c28c6c6cbc66f7d3cb8549e6d90522f27f2e5304214f2c9ef588c3</t>
+          <t>92b8ab9a449c6785e20a454b14ece0ebdbb3c4f2d3779352cf1439b2237fcc3c</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>dba29de70f28d13ce03f42b353730c7a0841ab76d892c3002e7a2e457feec960</t>
+          <t>b558a266d994e49fd41afe2d16642d7871bd88651956d7d8a4be5215f8c86007</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>5a90c4f2d8d4a94e7c60a04f3a1088899ef1e6160229d4e1a98e3ee9ed6f0a43</t>
+          <t>47b7f375f46b92c73dc212ee08b230021ce346468b3bd19d49bfd2013334edcb</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>f2559f4f2f86e25f77d3a9cded30a60c6bd5b4048461692ff382f09dd91e7dbf</t>
+          <t>f5bf02f4a8104cd7a9ef34f3ecde9f6386696f1af5829c08c8fa9b54e7cc07b1</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>11e4bf979f80415b420a73e1d52561fb9673e515a36225cf961b5625871d01ef</t>
+          <t>4a732d1cf38c61fae6b87396b04d24e6d007ac3e1f91ce51ac7a94571de4ed6e</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>37eb740001d74dcab194d6a4168598d45e4ab84e77cd1dfe6a55a07f40782849</t>
+          <t>40f6c01945c425f0bd812515352073541b9e65e96a37760ceed2da39fe3b2c6f</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>e96d6e039e7802c651269e09452d2a0d5f92f2cebdecbf6054bd63111e92ab1c</t>
+          <t>55181a323ef95b3bd296036f8333a74189398094ad921d3f283b62ece91b9dd9</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>975689cbc0a01c2e52ec3f88f5b90f182910c409af6f2504f4aa9f51e8d56a57</t>
+          <t>66be22dbdc0f2d6823fabd5c60872b0d88f642499eef2e1cc7c08f19b598f5b2</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>4393b098cdb1b5b6c5aca762172bd50798943f407b16565781cbf17c2e30c314</t>
+          <t>8b7ebb16be88d8fc4ee7bdc0e9c5c00dfb13f131e9bd438e980bf9b559c5d953</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>0ec893cace11b88af0679a97ebdd57e33e0387603c9267443655a6244024d0b2</t>
+          <t>fc1ae9c1b2f7bf9bbb3b113cf6fecb2a3604b3560ab1f2b62d4889873d4fd9e7</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>92b8ab9a449c6785e20a454b14ece0ebdbb3c4f2d3779352cf1439b2237fcc3c</t>
+          <t>c4d7f8afb7d77790371039cef72a367a81f566372a1fe7fc4dd0589f611aa204</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>b558a266d994e49fd41afe2d16642d7871bd88651956d7d8a4be5215f8c86007</t>
+          <t>af44181519a066260da1f4e15beed45980cbd7cdfef185f79ac23010bc38540e</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>47b7f375f46b92c73dc212ee08b230021ce346468b3bd19d49bfd2013334edcb</t>
+          <t>7794ecd95f5bb58e29f1bd4bff1d1a7e880f240e3b35fb069d26ae7a99503cce</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>f5bf02f4a8104cd7a9ef34f3ecde9f6386696f1af5829c08c8fa9b54e7cc07b1</t>
+          <t>019d5ab7caa19b2a9428e8ebc829eb326e4520d999424da98097f6a303418f34</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>4a732d1cf38c61fae6b87396b04d24e6d007ac3e1f91ce51ac7a94571de4ed6e</t>
+          <t>88c3693b633f8915eaa4ecf5cc78cc42dfff8b5e8a60a8d3bd8a933500c6be0e</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>40f6c01945c425f0bd812515352073541b9e65e96a37760ceed2da39fe3b2c6f</t>
+          <t>1c9a141b1db49da21c07335ad4692795b21d6d792c62be5d96e0a67f8a1431e9</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>55181a323ef95b3bd296036f8333a74189398094ad921d3f283b62ece91b9dd9</t>
+          <t>12a46bd2493233203b3bbe6685a54f3fc1f5386e57f47b99df005a0600501683</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>66be22dbdc0f2d6823fabd5c60872b0d88f642499eef2e1cc7c08f19b598f5b2</t>
+          <t>3aa8a07f1f31da8bfc47218eccaae318c8581d53520e60d72269754ef403328e</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>8b7ebb16be88d8fc4ee7bdc0e9c5c00dfb13f131e9bd438e980bf9b559c5d953</t>
+          <t>b68111b5701b82d29faedd0b0f036e4598d752591ccaff09237f3c45ab0817c0</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>fc1ae9c1b2f7bf9bbb3b113cf6fecb2a3604b3560ab1f2b62d4889873d4fd9e7</t>
+          <t>0e4012a7d57f8f098abb719c692318c45aa522fb0fb50412557bc7e328f0cf54</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>c4d7f8afb7d77790371039cef72a367a81f566372a1fe7fc4dd0589f611aa204</t>
+          <t>087b259db5ab477eeef6ec0007046d2bff66c1d2892f37fe71181241fd5f1910</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>af44181519a066260da1f4e15beed45980cbd7cdfef185f79ac23010bc38540e</t>
+          <t>54f2645634d8a59d1ea99eac9ae28960050704357e64184e0d03a4b6d079b3b6</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>7794ecd95f5bb58e29f1bd4bff1d1a7e880f240e3b35fb069d26ae7a99503cce</t>
+          <t>fe5f17743eb36cd33fe017841c6f8953a1bc67edd859021555fec9a3bcd4091e</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>019d5ab7caa19b2a9428e8ebc829eb326e4520d999424da98097f6a303418f34</t>
+          <t>6821f5be85475f963791f6cf111288074338715ccf7d272e43bb7c5981c2fa2c</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>88c3693b633f8915eaa4ecf5cc78cc42dfff8b5e8a60a8d3bd8a933500c6be0e</t>
+          <t>022cd466ac3b4eca8754d1bbcc1424d343f49e182fb8959db9503ac1c7fa39a0</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>1c9a141b1db49da21c07335ad4692795b21d6d792c62be5d96e0a67f8a1431e9</t>
+          <t>368c775503f24b07c334893285e9a69dbde6dae1b84d4fdb3750789d8c18dc77</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>12a46bd2493233203b3bbe6685a54f3fc1f5386e57f47b99df005a0600501683</t>
+          <t>55181a323ef95b3bd296036f8333a74189398094ad921d3f283b62ece91b9dd9</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>3aa8a07f1f31da8bfc47218eccaae318c8581d53520e60d72269754ef403328e</t>
+          <t>7cd183904e084b0e536546ac173c38d78972e41d764d66763699e9abc546959b</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>b68111b5701b82d29faedd0b0f036e4598d752591ccaff09237f3c45ab0817c0</t>
+          <t>a6f82a813493cfcc08e5b9401d111aa1793c6afc7428973964865f445118db13</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>0e4012a7d57f8f098abb719c692318c45aa522fb0fb50412557bc7e328f0cf54</t>
+          <t>4054d414135851f9cd65a33937acdf1ed9f5cc901ffabb3d779b4ee2c035e6a7</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>087b259db5ab477eeef6ec0007046d2bff66c1d2892f37fe71181241fd5f1910</t>
+          <t>e837bd2d30bcd15c9d8c4aa0e02673929e2b7fa3162cb8f3c933c5751d456143</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>54f2645634d8a59d1ea99eac9ae28960050704357e64184e0d03a4b6d079b3b6</t>
+          <t>a94059b8ecea96246acd1828e8e6eabf300e228215b9a2f514a6be372ce6a68b</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>66479f47bc851ef114a918a6ed5dc10813a207703973c5207d10999c6a2e2171</t>
+          <t>0c86e14f47e38d3100f6e1dffa9a2e6a22c761090807f90d0439c139fc5d0ba8</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>fe5f17743eb36cd33fe017841c6f8953a1bc67edd859021555fec9a3bcd4091e</t>
+          <t>28a403759f1c7ba5e95f86c89b7166d53f9aee95587b598bf081922a3bae6fa9</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>6821f5be85475f963791f6cf111288074338715ccf7d272e43bb7c5981c2fa2c</t>
+          <t>e62ae67ac1bfd675691220fecc6d3ff778fbfdc0512f60d17d96f67cba24e887</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>022cd466ac3b4eca8754d1bbcc1424d343f49e182fb8959db9503ac1c7fa39a0</t>
+          <t>c516100b4c8012dbe9af7740470660038ca2299a96c572a5cb5a25c479a3693b</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>368c775503f24b07c334893285e9a69dbde6dae1b84d4fdb3750789d8c18dc77</t>
+          <t>34c10a68d3c23196f829718065ed44587800a38205664b16ffa109b23f747d7a</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>7cd183904e084b0e536546ac173c38d78972e41d764d66763699e9abc546959b</t>
+          <t>2113c6e4a556c7ae783c439a19a180197ac471f94b8a0ac3982eb9ba2ff471a3</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>a6f82a813493cfcc08e5b9401d111aa1793c6afc7428973964865f445118db13</t>
+          <t>6c8d9cc67066b3c724b3b6712bd871b41908c8b38b6e64759e0a9db201236d35</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>4054d414135851f9cd65a33937acdf1ed9f5cc901ffabb3d779b4ee2c035e6a7</t>
+          <t>07d1cbcf0e2e37bfbcd7afcb2a5910e70e5dfbe24d8dba4e016d19c03a20f943</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>e837bd2d30bcd15c9d8c4aa0e02673929e2b7fa3162cb8f3c933c5751d456143</t>
+          <t>516f37024db65ff710dbf89606eb917b0b98d01423b966aecd796190639a58b9</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>a94059b8ecea96246acd1828e8e6eabf300e228215b9a2f514a6be372ce6a68b</t>
+          <t>12f43c0c3d2aad1490b270f90def5404d3f902349113ef24cb093d33df522611</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0c86e14f47e38d3100f6e1dffa9a2e6a22c761090807f90d0439c139fc5d0ba8</t>
+          <t>66479f47bc851ef114a918a6ed5dc10813a207703973c5207d10999c6a2e2171</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>28a403759f1c7ba5e95f86c89b7166d53f9aee95587b598bf081922a3bae6fa9</t>
+          <t>736dd72e94ad058ccfc9ce579a139754948ca1237b80fdd99d0af9c65e494494</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>e62ae67ac1bfd675691220fecc6d3ff778fbfdc0512f60d17d96f67cba24e887</t>
+          <t>7583dd7ca174656d19587b56baf2e86eebb737fdd76fe3ca2d9028b7382078df</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>c516100b4c8012dbe9af7740470660038ca2299a96c572a5cb5a25c479a3693b</t>
+          <t>efe10a95d5a88ff10b0783fa2ea0eb4a1ff6ef1f1a07ac40522c75f17a85025e</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>34c10a68d3c23196f829718065ed44587800a38205664b16ffa109b23f747d7a</t>
+          <t>ef647294a49e235ac70eb87a51995521176fc45771e6a17f1918b80a3c68a773</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>2113c6e4a556c7ae783c439a19a180197ac471f94b8a0ac3982eb9ba2ff471a3</t>
+          <t>1069cd537d4b14eb898b7933267e28cf9b79c62f1fcb2c6ec45ddf567b6a9359</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>6c8d9cc67066b3c724b3b6712bd871b41908c8b38b6e64759e0a9db201236d35</t>
+          <t>6b98ddd2f9376e6502ef209d87cafdd2e1c260366579c54767143697a0f66241</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>07d1cbcf0e2e37bfbcd7afcb2a5910e70e5dfbe24d8dba4e016d19c03a20f943</t>
+          <t>8c0316fcea2349390c0c27985537dd8f11904193033102a3666dbc392a61e337</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>516f37024db65ff710dbf89606eb917b0b98d01423b966aecd796190639a58b9</t>
+          <t>d98ef615876e5cbf4fdc71fac659fafc5bcd2e31168d0682cde2354d8682116a</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>12f43c0c3d2aad1490b270f90def5404d3f902349113ef24cb093d33df522611</t>
+          <t>8b434912c12d16a261436259259cbbe4db736e90abc21ad02ed0aa8af53f0021</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>736dd72e94ad058ccfc9ce579a139754948ca1237b80fdd99d0af9c65e494494</t>
+          <t>a550abb1e6dce4a0fabcb9d8e23cf0df74c825009d5b7bfa9e5477c220e71b3e</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>7583dd7ca174656d19587b56baf2e86eebb737fdd76fe3ca2d9028b7382078df</t>
+          <t>4bca4af3977f910372ebce3bf0bc4115cf66247484d4509661fcf8ee8323916e</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3062,14 +3062,14 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>efe10a95d5a88ff10b0783fa2ea0eb4a1ff6ef1f1a07ac40522c75f17a85025e</t>
+          <t>932a089c50c4b00158730fdcf81c02a58d665da84eee3b23ed9b622c4ff81c54</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>ef647294a49e235ac70eb87a51995521176fc45771e6a17f1918b80a3c68a773</t>
+          <t>8e4e9606ad2606a7749d8fd97dd555ad67bf2ca3562b18d413df6ac16265be88</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>55181a323ef95b3bd296036f8333a74189398094ad921d3f283b62ece91b9dd9</t>
+          <t>01924975dad6af70efff20a7a5e4a6dcbf28a08b8f10de753a9271b637451965</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>1069cd537d4b14eb898b7933267e28cf9b79c62f1fcb2c6ec45ddf567b6a9359</t>
+          <t>5088f788be15084248f1ee871879474c0c207562e2e55026af325462151028e7</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>6b98ddd2f9376e6502ef209d87cafdd2e1c260366579c54767143697a0f66241</t>
+          <t>cac3c64431c69bba0fb6ebba5efa10eb80f6636a986a9bf15e7d03e0319c7e9f</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>8c0316fcea2349390c0c27985537dd8f11904193033102a3666dbc392a61e337</t>
+          <t>6cd265c7e87cf442dfa12b8339326b90523dc86cb2be981cc12198709db3ef5e</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>d98ef615876e5cbf4fdc71fac659fafc5bcd2e31168d0682cde2354d8682116a</t>
+          <t>c6d513558b4454b3fdbb584d194113a0ad8c2437a048952044d54597e0bfc576</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>8b434912c12d16a261436259259cbbe4db736e90abc21ad02ed0aa8af53f0021</t>
+          <t>2f37639795782f662281cec380aa48735411ec40b52d17be3c52da82d554e499</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>a550abb1e6dce4a0fabcb9d8e23cf0df74c825009d5b7bfa9e5477c220e71b3e</t>
+          <t>031c71239960edd7534e77a462021bb57ba477ebedaac2fef5696c2cd2aee09f</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>4bca4af3977f910372ebce3bf0bc4115cf66247484d4509661fcf8ee8323916e</t>
+          <t>0b616ccf4e4b7a88e19dbf4b9110f432ae622698df17352c4d951a8446663156</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>932a089c50c4b00158730fdcf81c02a58d665da84eee3b23ed9b622c4ff81c54</t>
+          <t>7e89428fe963c1f1cfabfb041a5e49aa72a45eb5fe86e915da4366df2dec5768</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>8e4e9606ad2606a7749d8fd97dd555ad67bf2ca3562b18d413df6ac16265be88</t>
+          <t>0da5893570278ae78f143171d98c6061761bfe5e46d884d1aa5feed289f1e82e</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>5088f788be15084248f1ee871879474c0c207562e2e55026af325462151028e7</t>
+          <t>c00885958d5959a9cc2f8c0677407e0b521714c7ebc380cfa7f09de0c8a10908</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>cac3c64431c69bba0fb6ebba5efa10eb80f6636a986a9bf15e7d03e0319c7e9f</t>
+          <t>4b5066c60a2968eedb517828e0f3d112e0f3b58c0715e7a8b4ce427a9ee5be77</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>6cd265c7e87cf442dfa12b8339326b90523dc86cb2be981cc12198709db3ef5e</t>
+          <t>b4395b594aea41d0e30bbdcc882f533a3f3019ce92ef88c4c0192415c42cb54b</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>c6d513558b4454b3fdbb584d194113a0ad8c2437a048952044d54597e0bfc576</t>
+          <t>1c0272cc58f6e2b726c8b986d5fa159397b3d60599cff1075d9a25af8f8d10b7</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>2f37639795782f662281cec380aa48735411ec40b52d17be3c52da82d554e499</t>
+          <t>c3e8af6990252d883551a9b1a3863f11ffd71367566eb77e7067d770e8413c39</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>031c71239960edd7534e77a462021bb57ba477ebedaac2fef5696c2cd2aee09f</t>
+          <t>b6b6e63c8b918ed7a8c32c4766b5cedbee6dc4aac6f984690218f6b1e6de4d74</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>0b616ccf4e4b7a88e19dbf4b9110f432ae622698df17352c4d951a8446663156</t>
+          <t>cf29c1fd408a45e5455aa4ab0cc5baf733a2c5b1ef4614cad96867f2760949a2</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>7e89428fe963c1f1cfabfb041a5e49aa72a45eb5fe86e915da4366df2dec5768</t>
+          <t>a54aa7900a9c0cb41248be8ef53308afda162d0521ad0f0dda80075dc879d391</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>0da5893570278ae78f143171d98c6061761bfe5e46d884d1aa5feed289f1e82e</t>
+          <t>a36aec88e4831676313b4a981fa6060a6edf1b8e366c39465f6aa683ac113649</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>01924975dad6af70efff20a7a5e4a6dcbf28a08b8f10de753a9271b637451965</t>
+          <t>bf8a1d609999870baad5551e4dec7a776bf61002e9dd57fc2a6d1c1a7cd9390b</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>c00885958d5959a9cc2f8c0677407e0b521714c7ebc380cfa7f09de0c8a10908</t>
+          <t>5854620f530b50d831166cf3d8eacfdfcf9b05cf423c1e54ac477e5059ab18cc</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>4b5066c60a2968eedb517828e0f3d112e0f3b58c0715e7a8b4ce427a9ee5be77</t>
+          <t>8d182c98edf2a77dbb3f646a6b655643e00251718979b7cd7fdf897ba71467f1</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>b4395b594aea41d0e30bbdcc882f533a3f3019ce92ef88c4c0192415c42cb54b</t>
+          <t>48eaf90a12709129ac352b2ca5a99487959e5935534129c3d04d111051ad9591</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>1c0272cc58f6e2b726c8b986d5fa159397b3d60599cff1075d9a25af8f8d10b7</t>
+          <t>a82a710e2d457e21bbf4d86b7137a7b00beeacb8f837159650bb9a772cb32394</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>c3e8af6990252d883551a9b1a3863f11ffd71367566eb77e7067d770e8413c39</t>
+          <t>1bcb5f6792b27c0f0e81ea5f3e30ff6285ae0450d260f78fb6b6078be6653356</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>b6b6e63c8b918ed7a8c32c4766b5cedbee6dc4aac6f984690218f6b1e6de4d74</t>
+          <t>0c1b4da45c331e8aed1a53c61256c984468ec5f20ae4f5080ac96f14928386fc</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>cf29c1fd408a45e5455aa4ab0cc5baf733a2c5b1ef4614cad96867f2760949a2</t>
+          <t>1e9d61db3bd5cab9be45a38e626d022c3d5e9b0c65f25795b1f6dc8b800da1c6</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>a54aa7900a9c0cb41248be8ef53308afda162d0521ad0f0dda80075dc879d391</t>
+          <t>81d086a64764f682ad938b6a41be87b73e8d48e8d792519bfc73e5ab1c31eb64</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>a36aec88e4831676313b4a981fa6060a6edf1b8e366c39465f6aa683ac113649</t>
+          <t>9f55eea5012fe8b8cfa6bc9ff8c94d5ee362230fddc03f1936ff7028d86bd0a4</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>5854620f530b50d831166cf3d8eacfdfcf9b05cf423c1e54ac477e5059ab18cc</t>
+          <t>ee841840a3694cbf985af7360c1c5cda4c4d545b5d1143d8ab51121d5fd50dc2</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>8d182c98edf2a77dbb3f646a6b655643e00251718979b7cd7fdf897ba71467f1</t>
+          <t>bd465d2311e927a7580dcb1fe47f975ada5fe86d65eb46aaaa0e21bdf79724fc</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>48eaf90a12709129ac352b2ca5a99487959e5935534129c3d04d111051ad9591</t>
+          <t>0647d43b39e864ff0c2ff8bf0b17606b9bd66d559df437bff6e4343de6463b2e</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>a82a710e2d457e21bbf4d86b7137a7b00beeacb8f837159650bb9a772cb32394</t>
+          <t>e209cae860f0ab4081fe12df226261064d5dda1b6f8610820bd2181d805ebe6d</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>1bcb5f6792b27c0f0e81ea5f3e30ff6285ae0450d260f78fb6b6078be6653356</t>
+          <t>6a7695b29e3a6e813c89ecad70f23a4f22521227ea79bea25750dee4086082dd</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0c1b4da45c331e8aed1a53c61256c984468ec5f20ae4f5080ac96f14928386fc</t>
+          <t>e44834321dc34c7675bbe1edc927c515c69e6339dc0a2be015ab74cd70e649f5</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>1e9d61db3bd5cab9be45a38e626d022c3d5e9b0c65f25795b1f6dc8b800da1c6</t>
+          <t>b1d1cf4949ea5ea03de3b5b3f98630ff7da96d47500fb3ee72f68a9b6f98e09c</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>81d086a64764f682ad938b6a41be87b73e8d48e8d792519bfc73e5ab1c31eb64</t>
+          <t>d186d27ca673047a2eecaa5c3a5c52e74a630f556785f903bb3c8e810df0e839</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>9f55eea5012fe8b8cfa6bc9ff8c94d5ee362230fddc03f1936ff7028d86bd0a4</t>
+          <t>0852febf9a30cdd067a8e87eea5a26bdb5768ec7314b023ff999699940981bd8</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>ee841840a3694cbf985af7360c1c5cda4c4d545b5d1143d8ab51121d5fd50dc2</t>
+          <t>7e7216d1f62607b70993efce5c068bac5ffd3fc029a53dca0ba817d08c7e073f</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>bd465d2311e927a7580dcb1fe47f975ada5fe86d65eb46aaaa0e21bdf79724fc</t>
+          <t>d735696efe1ffb7377a63eb8ce25a6a896eb8c7c27ed6a83a2d202adb27701ee</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>0647d43b39e864ff0c2ff8bf0b17606b9bd66d559df437bff6e4343de6463b2e</t>
+          <t>718ba6ecbbb27484cd5a61aac7e1faff9a18e61372520dfb7866dec615f2858c</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>e209cae860f0ab4081fe12df226261064d5dda1b6f8610820bd2181d805ebe6d</t>
+          <t>36cf591dcd9fdac56c3906217db9cc068fbd630225ebf04b69352ffc6a341fe0</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>6a7695b29e3a6e813c89ecad70f23a4f22521227ea79bea25750dee4086082dd</t>
+          <t>3b42ee10340273a8e846a69084d4898682d9a4de76d6317574a5e33937a2f306</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>e44834321dc34c7675bbe1edc927c515c69e6339dc0a2be015ab74cd70e649f5</t>
+          <t>b40bacec50aeb16f7215957776df0ca18e860125fa7d32cf00f60988a20253a0</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>b1d1cf4949ea5ea03de3b5b3f98630ff7da96d47500fb3ee72f68a9b6f98e09c</t>
+          <t>aeed42ceb00742979b70ef77975d6fd19e75fbc40904156380efd2621490ecd8</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>d186d27ca673047a2eecaa5c3a5c52e74a630f556785f903bb3c8e810df0e839</t>
+          <t>55675fbef0c6392c91545b767f7d4f4f5a5a28eb3e35c8e280f61a70a8b5f854</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>0852febf9a30cdd067a8e87eea5a26bdb5768ec7314b023ff999699940981bd8</t>
+          <t>51932588dceda70129a7f4204d9bba70814125d7d3e9cad1837ee5ec62c5cb82</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>7e7216d1f62607b70993efce5c068bac5ffd3fc029a53dca0ba817d08c7e073f</t>
+          <t>6effa2bd9b0d41a12414c0547023fb8734d0a806ddd679ef9fde23e2d0e94ee1</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>d735696efe1ffb7377a63eb8ce25a6a896eb8c7c27ed6a83a2d202adb27701ee</t>
+          <t>03e31558a2f786e83d11e3cd84fe5aac3ab88f0c8ce25aaace4b5893aa4609cc</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>718ba6ecbbb27484cd5a61aac7e1faff9a18e61372520dfb7866dec615f2858c</t>
+          <t>004b68eec37c3ea66ac6fe6bff32a1073c98047e1c5ab83da969fd812281132f</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>36cf591dcd9fdac56c3906217db9cc068fbd630225ebf04b69352ffc6a341fe0</t>
+          <t>71937062dd22418c2b64bb52091831567511657d54a1176ccf6abb3277f236be</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>3b42ee10340273a8e846a69084d4898682d9a4de76d6317574a5e33937a2f306</t>
+          <t>1083509c2e881271d2e12bc4367c82832016688e5095846a5728590919cb164d</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>b40bacec50aeb16f7215957776df0ca18e860125fa7d32cf00f60988a20253a0</t>
+          <t>091ddf22a468fb6324727f90cd5fb5d71018b601442066cfdaeb6ab282047743</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>aeed42ceb00742979b70ef77975d6fd19e75fbc40904156380efd2621490ecd8</t>
+          <t>7785fe3eb0edd7866524cc73accfa4d2541770de0817cd17aeec2c946061aa7c</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>55675fbef0c6392c91545b767f7d4f4f5a5a28eb3e35c8e280f61a70a8b5f854</t>
+          <t>9c65aba427d937a1d00d2095ef44e6ed7510b1927d63f69035cbc1f51cfaadd1</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>51932588dceda70129a7f4204d9bba70814125d7d3e9cad1837ee5ec62c5cb82</t>
+          <t>985eec6e1b9d234c01cfb18710cbc755e9dd1263674096dd662cbed95708738e</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>bf8a1d609999870baad5551e4dec7a776bf61002e9dd57fc2a6d1c1a7cd9390b</t>
+          <t>025390df624e2860f4cc353ca794dfa8ec8f247ba2fb3ebf5d47d7bae3b06fe5</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>6effa2bd9b0d41a12414c0547023fb8734d0a806ddd679ef9fde23e2d0e94ee1</t>
+          <t>269e8dbd432ccad5dcd042950ce694b9b7867801cc69a98c13f26aad281ec8d5</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>03e31558a2f786e83d11e3cd84fe5aac3ab88f0c8ce25aaace4b5893aa4609cc</t>
+          <t>1d469f3e91114458c67de4815ec38666b0c52ad8009e46e2aefc638a80881dbb</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>004b68eec37c3ea66ac6fe6bff32a1073c98047e1c5ab83da969fd812281132f</t>
+          <t>90437ef678ae3777ce158781de56762d66e791566a3756fe7cbd93184ae16e69</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>71937062dd22418c2b64bb52091831567511657d54a1176ccf6abb3277f236be</t>
+          <t>296457fdacfaf9cdca35efab41340d7e8fb2be326ce2ed987c74e6049f84d36c</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>1083509c2e881271d2e12bc4367c82832016688e5095846a5728590919cb164d</t>
+          <t>3a6fd82b21d270c2a6ce15a22afc5facd5dec270a4c4b668421bd4a391038569</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>091ddf22a468fb6324727f90cd5fb5d71018b601442066cfdaeb6ab282047743</t>
+          <t>6078d27d5b910d3cf8ff567ecc0af6d8cb46b7bce47720b3acfc3c91e2cb6c25</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>7785fe3eb0edd7866524cc73accfa4d2541770de0817cd17aeec2c946061aa7c</t>
+          <t>e8cf193a384b71d2e3eb96fead48286709bdbef4e20012435efe8bd114417e69</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>9c65aba427d937a1d00d2095ef44e6ed7510b1927d63f69035cbc1f51cfaadd1</t>
+          <t>3ee76b1c563f0b49f681540cba0c192647df7043d052de04635961594d8b8ab7</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>985eec6e1b9d234c01cfb18710cbc755e9dd1263674096dd662cbed95708738e</t>
+          <t>bd42e2f606dccf28ff6d8d5beae818091b2cabfb29919e230449c5c597116180</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>025390df624e2860f4cc353ca794dfa8ec8f247ba2fb3ebf5d47d7bae3b06fe5</t>
+          <t>13640350169e926eeeae8f219096eea3566d9de37934273ee5f5f6d85e635324</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>269e8dbd432ccad5dcd042950ce694b9b7867801cc69a98c13f26aad281ec8d5</t>
+          <t>4c416298873c69bc33b901b510a146be8e88f71f780b3d046cb4f90c086e33ed</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>1d469f3e91114458c67de4815ec38666b0c52ad8009e46e2aefc638a80881dbb</t>
+          <t>aed2ebbb32865463cc0e631b0063fc6a5e9a114fd1ceeb16f1a672d0dc9e63c7</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>90437ef678ae3777ce158781de56762d66e791566a3756fe7cbd93184ae16e69</t>
+          <t>c7721aa3a3bb4f38717d440172eb86f881d26c115c5021d497a4babf4f68d4d3</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>296457fdacfaf9cdca35efab41340d7e8fb2be326ce2ed987c74e6049f84d36c</t>
+          <t>fc3191bca527b1a7dc58cde9a8a77cc83fa5c848a0821fa4df3008b71bafc26f</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>3a6fd82b21d270c2a6ce15a22afc5facd5dec270a4c4b668421bd4a391038569</t>
+          <t>2b1b376cc4384c481d789f62049d4ca42530034d0d03d8b2f67ef2a753bd8184</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>6078d27d5b910d3cf8ff567ecc0af6d8cb46b7bce47720b3acfc3c91e2cb6c25</t>
+          <t>ac70c12e147a47125c249cde9e87dee6edb940d83d68a73c50e0a5662ca98189</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>e8cf193a384b71d2e3eb96fead48286709bdbef4e20012435efe8bd114417e69</t>
+          <t>b463e03dea93b72e8af7c2e374573b5736ff817bc2eb9243da9207a6ded9d8ab</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>3ee76b1c563f0b49f681540cba0c192647df7043d052de04635961594d8b8ab7</t>
+          <t>02ff42d503b5a8d2c5697f87f036b78974ca84f91eef63409eb06d1e9ad690ce</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>bd42e2f606dccf28ff6d8d5beae818091b2cabfb29919e230449c5c597116180</t>
+          <t>09395af0e99eff504022a6e3efabe87347e943a7fe1f46d793d5e29fd59bdd85</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>13640350169e926eeeae8f219096eea3566d9de37934273ee5f5f6d85e635324</t>
+          <t>8edd3be414338e3d83912368e6874b06cf173af1e40946134ac2bb5ecfe62cff</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>4c416298873c69bc33b901b510a146be8e88f71f780b3d046cb4f90c086e33ed</t>
+          <t>0d98f22652e27e640bbb8bca23d7a7c30feba724abd36d519362d193f77a0620</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>aed2ebbb32865463cc0e631b0063fc6a5e9a114fd1ceeb16f1a672d0dc9e63c7</t>
+          <t>6eeb2b98fa6bc213842036cbecc203f6af41fea8cffd3598ba87393a25ef1250</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>c7721aa3a3bb4f38717d440172eb86f881d26c115c5021d497a4babf4f68d4d3</t>
+          <t>c576de0a5be664b858b290aa94eebbaef05fae3c5e8c6d333538e7c1a78335ef</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>fc3191bca527b1a7dc58cde9a8a77cc83fa5c848a0821fa4df3008b71bafc26f</t>
+          <t>d773d317a33405d2157adc5984d088cb864c78fcab643e49cca371ee59fba005</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>2b1b376cc4384c481d789f62049d4ca42530034d0d03d8b2f67ef2a753bd8184</t>
+          <t>d1c8df00b5463ef315a7e640d7dbd4f19be8143839ec20ced44d7cda327051ed</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>ac70c12e147a47125c249cde9e87dee6edb940d83d68a73c50e0a5662ca98189</t>
+          <t>0fcad3f8aa63df1bf337f2ce8775011948ca72314703436e9d951d8807e70f82</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>b463e03dea93b72e8af7c2e374573b5736ff817bc2eb9243da9207a6ded9d8ab</t>
+          <t>20f3b5d16404b144deee1feb6e3373962c383ab29cfcac0572446f3e38d4a4ce</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>02ff42d503b5a8d2c5697f87f036b78974ca84f91eef63409eb06d1e9ad690ce</t>
+          <t>3f8ad01e1bb247ea302d8a8fc8c36f112d33686eb95ef446f7d7fadec0a9f633</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>09395af0e99eff504022a6e3efabe87347e943a7fe1f46d793d5e29fd59bdd85</t>
+          <t>7ec74e78dc0208dd2f55a8c6f0d6cfc678b91ff15d474393d8d91237c3105dda</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>8edd3be414338e3d83912368e6874b06cf173af1e40946134ac2bb5ecfe62cff</t>
+          <t>294c50972c24f8e8ca370c86f2b4c2a5c9d4f163f118e36fb56c879139c38b07</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>0d98f22652e27e640bbb8bca23d7a7c30feba724abd36d519362d193f77a0620</t>
+          <t>18d904f5b7ae406217394ab2253fdfcae8c980532c9e4b39a66eff87829ff53f</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>6eeb2b98fa6bc213842036cbecc203f6af41fea8cffd3598ba87393a25ef1250</t>
+          <t>c47983ccaa6baaf144fdf8b4d6de3f81a7406f419924e26d31f30597c1821e25</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>c576de0a5be664b858b290aa94eebbaef05fae3c5e8c6d333538e7c1a78335ef</t>
+          <t>105fa62d6a5b041e549859f34e9a7050b7166836c4cd21c138312a9bb3bd30d9</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>d773d317a33405d2157adc5984d088cb864c78fcab643e49cca371ee59fba005</t>
+          <t>a874b53c286830a38114ca6c3e78197711f030e036c97ff0d1b16787253b126a</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>d1c8df00b5463ef315a7e640d7dbd4f19be8143839ec20ced44d7cda327051ed</t>
+          <t>c36fa51cc4f525f033d6ad0882960952d1fc309e622b17cf605664bff4b987c6</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>0fcad3f8aa63df1bf337f2ce8775011948ca72314703436e9d951d8807e70f82</t>
+          <t>b0e993674c053454a0b9e31d822d0fdfa925bea7b4ea689f881c3038af16b020</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>7bb7f04d08c3e2a2829f673b71b9740b07cf2a1b6509111d91c2080ee5c5064b</t>
+          <t>af6a2c7cd5e843236b925503e83562a77e378610e6ff3aada88473cff44f09c6</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>20f3b5d16404b144deee1feb6e3373962c383ab29cfcac0572446f3e38d4a4ce</t>
+          <t>034094a77895bef79502f557f6e3016cfb7ea55da19c2b9e1fc8da1b10473970</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>3f8ad01e1bb247ea302d8a8fc8c36f112d33686eb95ef446f7d7fadec0a9f633</t>
+          <t>e2db4b70f83f95b98c253a07e9da48354c8a927f17cbd17dfa2d7229b7b09c70</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>edb43f9e32a80e615d17b187574a731aedadf1cc41308492e83f7188d6f785c0</t>
+          <t>1011576eb2cd675bcc7b776379f93e2f0f3dce1405c2e1ff9fa9658e3bd0410d</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>7ec74e78dc0208dd2f55a8c6f0d6cfc678b91ff15d474393d8d91237c3105dda</t>
+          <t>4fa4eb25d9b2db17b9293d83750c3e126674177d27bc6b0fbb1d29a517426b6d</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>4727c9a0937c54b50242c8927e5e3222cc2b988117ef9533ad4dd8d4d8149bc9</t>
+          <t>8223303ec9edaf5fa9cce801aa45051410344c459add8587d6a39849c653f4b0</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>294c50972c24f8e8ca370c86f2b4c2a5c9d4f163f118e36fb56c879139c38b07</t>
+          <t>2e4e492768f5f8e42ec95842e01d4eda5e112d732b743b2d247a8f9bac620305</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>00433fe89c5d446ea01c2a19f069f7a20bbc44e565f3c592ef782fd7274ea68f</t>
+          <t>ede1e1eb1eef75919b897e2261fe680d3771122c61206ec1b9c9742183657084</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>18d904f5b7ae406217394ab2253fdfcae8c980532c9e4b39a66eff87829ff53f</t>
+          <t>7a75415a6366efb3ecf2b6f65437c257944ce5c22d3239746b3eb23cc6631766</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>43b5003fc43e0b7526cd65501f301cd099980f9f0c8bcb1a2de954577db9f4d4</t>
+          <t>3e706b0b2c3666117fb00fb5e92b9d9cd6352431d95ffb0fbcfe586b48be3952</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>7acf8db892da674ac9478408ce8f55ea6335882f2f7d08d44d2757a2597761a1</t>
+          <t>f26f6c64e66ef4a9583a8933816c06ea5f1bc38fffcdb6bb5b083ad05862ef69</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>5668ef26abc52f6ccc3d69db8c1cbc41a6c21ec6dbd0417d5ac54244109b7754</t>
+          <t>1451d9af565f022368cd3fd6e8c475da0ab5f0e00888f5a23241e5e22a3f3249</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>037015d69e9d63ff13f3cccb7fb2adbf4e1fac24eeabdc92a9195a4c16083f7c</t>
+          <t>f4f1bebad9cfef4bd1aa246fb1d75fb8d51ebf7838e45b11a7210384c99c9c2a</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>c47983ccaa6baaf144fdf8b4d6de3f81a7406f419924e26d31f30597c1821e25</t>
+          <t>153baf2fa5de129824595b1c52281bff2ea422139f071d5a56387bbee4015814</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>105fa62d6a5b041e549859f34e9a7050b7166836c4cd21c138312a9bb3bd30d9</t>
+          <t>f359a0eb99a319c35dcee04f7478b75b81192bef23bbed78e07db1ce277915f6</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>a874b53c286830a38114ca6c3e78197711f030e036c97ff0d1b16787253b126a</t>
+          <t>f2d322a2e71cd513faa5a953515f9ffe1d6b867c1af6ee186bb63cdaab1e6ad6</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>c36fa51cc4f525f033d6ad0882960952d1fc309e622b17cf605664bff4b987c6</t>
+          <t>dfba921a4909bae2ff85116cf7700e1cab737c258536823c59d0a4aa3ed06194</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>66479f47bc851ef114a918a6ed5dc10813a207703973c5207d10999c6a2e2171</t>
+          <t>6b974e694cc2bd55f50111111ccd25b147d20e447c4880e068336fa4fa4e559b</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>b0e993674c053454a0b9e31d822d0fdfa925bea7b4ea689f881c3038af16b020</t>
+          <t>9815e63be81ec02bde81b8e6630a89fa6caa96421f69307094b4f5b8a3ac9301</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>034094a77895bef79502f557f6e3016cfb7ea55da19c2b9e1fc8da1b10473970</t>
+          <t>60d9d834bfd657f5184b0ee7f15fb8c37bf25daec3d3ebf586c8356b16cbd165</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>e2db4b70f83f95b98c253a07e9da48354c8a927f17cbd17dfa2d7229b7b09c70</t>
+          <t>ff195fd1e51059079082b09eaf6b5d611282ffd48eeea4b2c7967562cacf0e8a</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>4fa4eb25d9b2db17b9293d83750c3e126674177d27bc6b0fbb1d29a517426b6d</t>
+          <t>a495977261815522bd2d2328078ce59b79ab55a3a7b597b5f6a882c3121dfabd</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>2e4e492768f5f8e42ec95842e01d4eda5e112d732b743b2d247a8f9bac620305</t>
+          <t>480a14d4738f836df92058611fe8f037b02210a7d516af7e9da4ba9df4f50d6c</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>7a75415a6366efb3ecf2b6f65437c257944ce5c22d3239746b3eb23cc6631766</t>
+          <t>87273c3b221bb0f6f1bff7e2ad3a3d04c3ca118ec65e5470fedb24eb0564a561</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>153baf2fa5de129824595b1c52281bff2ea422139f071d5a56387bbee4015814</t>
+          <t>da7e5487108aff496270c3b38587724610de203e2bfabb0f746957bee37a54d2</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>f359a0eb99a319c35dcee04f7478b75b81192bef23bbed78e07db1ce277915f6</t>
+          <t>7aea6a64baf640e878758131052f8858124e612bea2965189d0b5af3d3042e8b</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>f2d322a2e71cd513faa5a953515f9ffe1d6b867c1af6ee186bb63cdaab1e6ad6</t>
+          <t>393b040b4630365553c2f767a1140d5c1b47e8a13b67c2d16532488ae27b1114</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>dfba921a4909bae2ff85116cf7700e1cab737c258536823c59d0a4aa3ed06194</t>
+          <t>4d9396b0f68f43101989118b90b82bba3e6435e1c4ba816576b797985961ab24</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>9815e63be81ec02bde81b8e6630a89fa6caa96421f69307094b4f5b8a3ac9301</t>
+          <t>a349463fe0e73766a861424d013b613dc96c99e8d49625be32913eb177ce9438</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>af6a2c7cd5e843236b925503e83562a77e378610e6ff3aada88473cff44f09c6</t>
+          <t>706cee54cff03c0a3b7373943799807a607295217b200cdf559066a5075da910</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>60d9d834bfd657f5184b0ee7f15fb8c37bf25daec3d3ebf586c8356b16cbd165</t>
+          <t>510c94b5f52e5faa66e6422ed65412bec59606b031e8e9dec9da05bb048ba7e2</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>ff195fd1e51059079082b09eaf6b5d611282ffd48eeea4b2c7967562cacf0e8a</t>
+          <t>441b6b51a41e49a7d43de3a614e527cc1217d116d826a62fdb0b5a767488e07f</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1011576eb2cd675bcc7b776379f93e2f0f3dce1405c2e1ff9fa9658e3bd0410d</t>
+          <t>a3cbd0393a9b1b3772dd04e737cc62f31a21c3487c87043225b0a5a47c242b11</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>a495977261815522bd2d2328078ce59b79ab55a3a7b597b5f6a882c3121dfabd</t>
+          <t>c35debacf43af823fff405191b10651d3e67f0c45c29acf81f8e5a25c15e95df</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>8223303ec9edaf5fa9cce801aa45051410344c459add8587d6a39849c653f4b0</t>
+          <t>f52d40417c2a389983067164256784acfbc58f1e3efa5f8124e1f94880ca93d0</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>480a14d4738f836df92058611fe8f037b02210a7d516af7e9da4ba9df4f50d6c</t>
+          <t>b2957a3b162108b296332f6b0358f22a2345e2d8f67540f948fcc18d26528b5c</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>ede1e1eb1eef75919b897e2261fe680d3771122c61206ec1b9c9742183657084</t>
+          <t>79f5348bf6fb0757eb312fd8e1afce108b0f4d69c4af347cdec7331c9db7009e</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>87273c3b221bb0f6f1bff7e2ad3a3d04c3ca118ec65e5470fedb24eb0564a561</t>
+          <t>6ce3f25de2e64a90381ba1f53cf84926f026a210c67a317d18125d837eab7c07</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>3e706b0b2c3666117fb00fb5e92b9d9cd6352431d95ffb0fbcfe586b48be3952</t>
+          <t>b08f308c7596e1a726598466407890b4697b8f1fc6bee3f032deacd9dce98ad6</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>f26f6c64e66ef4a9583a8933816c06ea5f1bc38fffcdb6bb5b083ad05862ef69</t>
+          <t>b1b40454886742cdee40466f8ad9a473ed8431a4c37db8590e01d876fd058480</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>1451d9af565f022368cd3fd6e8c475da0ab5f0e00888f5a23241e5e22a3f3249</t>
+          <t>5d9f4fce6397a17ef807ce5775af71418bf83c13e8e318d1ace21ebf5312b39b</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>f4f1bebad9cfef4bd1aa246fb1d75fb8d51ebf7838e45b11a7210384c99c9c2a</t>
+          <t>99a11b30d6fd2f5a82e49eb509e7100cd5fb42c869e5d7816a903d8d0aeda108</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>da7e5487108aff496270c3b38587724610de203e2bfabb0f746957bee37a54d2</t>
+          <t>1d28e25a7e5859fd4a23b65364113ffb996f12ca7756ba3fa159b5d9ef8e17d3</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>7aea6a64baf640e878758131052f8858124e612bea2965189d0b5af3d3042e8b</t>
+          <t>027ed66a1c556aa2828977191fb82faa752e25908924fa535a7cd20aacda16fb</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>393b040b4630365553c2f767a1140d5c1b47e8a13b67c2d16532488ae27b1114</t>
+          <t>982abe391ce00aa30304154c2c5594985b30df67d4b466dbe2fd116e9479847e</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>4d9396b0f68f43101989118b90b82bba3e6435e1c4ba816576b797985961ab24</t>
+          <t>cd7cf9720b6ff29e1b39928bc6d0dc9ddc325cd20b202cd8c4b9ecaa5cbb12c2</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>6b974e694cc2bd55f50111111ccd25b147d20e447c4880e068336fa4fa4e559b</t>
+          <t>b318ebc9334707988b9b569f5e3bb75d853e5bf40bf8db8eea7307267dd4352e</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>a349463fe0e73766a861424d013b613dc96c99e8d49625be32913eb177ce9438</t>
+          <t>e56026a6ce5d1a97a8995fbe9fdc91cf647bd8ab44ecf883b0464c8177e17814</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>706cee54cff03c0a3b7373943799807a607295217b200cdf559066a5075da910</t>
+          <t>91b9130693881d9019f4c0291a0c314fd5d74f145d77b621af89b2cd1f158588</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>510c94b5f52e5faa66e6422ed65412bec59606b031e8e9dec9da05bb048ba7e2</t>
+          <t>be3ba1de4dbe12eaca9e04aa0021ac0ff722da7d6dae962af109ca073eab57ef</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>441b6b51a41e49a7d43de3a614e527cc1217d116d826a62fdb0b5a767488e07f</t>
+          <t>1a06b1c88498f4efbfb16b94840fdb2c33f92629c192fd892cfe81bb18af69e6</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>a3cbd0393a9b1b3772dd04e737cc62f31a21c3487c87043225b0a5a47c242b11</t>
+          <t>a7650ad9f27b10aa755b8f65c55d337d610649fb6dca61af7a851533d37a799d</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>c35debacf43af823fff405191b10651d3e67f0c45c29acf81f8e5a25c15e95df</t>
+          <t>f001d27820947b2fcb585c6151a47bf582c06c646d943a67efa70fdeb9931700</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>f52d40417c2a389983067164256784acfbc58f1e3efa5f8124e1f94880ca93d0</t>
+          <t>e30485ea546242993ae2abb1103aac82a01f87b7a9f6a6c5053f6d7e6753c42b</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>b2957a3b162108b296332f6b0358f22a2345e2d8f67540f948fcc18d26528b5c</t>
+          <t>eb385cdbec517b9b7fe66967347b07bbdd3d026c279da239df0bda5ad282dded</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>79f5348bf6fb0757eb312fd8e1afce108b0f4d69c4af347cdec7331c9db7009e</t>
+          <t>24980391d43381a0476212cb47bdc60edc3939f9e5aedc367fc81e4fd2533df7</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>6ce3f25de2e64a90381ba1f53cf84926f026a210c67a317d18125d837eab7c07</t>
+          <t>1dbe19ecdb75809e98475461310d66a74f45bd671a96c709d141d2ed49d1b01c</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>b08f308c7596e1a726598466407890b4697b8f1fc6bee3f032deacd9dce98ad6</t>
+          <t>c215cf3a9b646b51447778ad47f711a6b4b938aa815b2a64c45c2186bbb54a83</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>b1b40454886742cdee40466f8ad9a473ed8431a4c37db8590e01d876fd058480</t>
+          <t>d66fdec05c74ddc5190228772045ea75cf909373c695e5017995661a28ae4e72</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>5d9f4fce6397a17ef807ce5775af71418bf83c13e8e318d1ace21ebf5312b39b</t>
+          <t>04b94cc8367135308045beb56773b7fe10e014baa6f26e663dd40866dac72bdc</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>99a11b30d6fd2f5a82e49eb509e7100cd5fb42c869e5d7816a903d8d0aeda108</t>
+          <t>cbbc4b8fd4d80bded6cf61d6a7280145983ed2d1f59aa36bc414d4a4b05fe919</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>1d28e25a7e5859fd4a23b65364113ffb996f12ca7756ba3fa159b5d9ef8e17d3</t>
+          <t>ae55e00c0703490c41f3b0474066c123dff836bfb6dc1d98317b5bb715e272f1</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>027ed66a1c556aa2828977191fb82faa752e25908924fa535a7cd20aacda16fb</t>
+          <t>13d63efa203a9a7c1a085eb9d73ea9d6e565f2ffb6ae0329143b9458d9f47ca2</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>982abe391ce00aa30304154c2c5594985b30df67d4b466dbe2fd116e9479847e</t>
+          <t>68c3a6839d61dd3ae5af3f04fc980cd194b92a4e93f9c129b472a5277ef60a00</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>cd7cf9720b6ff29e1b39928bc6d0dc9ddc325cd20b202cd8c4b9ecaa5cbb12c2</t>
+          <t>62d9f42159a69ea68d4adc24272bce03b9f9c5ca0704728a71787798622839d5</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>b318ebc9334707988b9b569f5e3bb75d853e5bf40bf8db8eea7307267dd4352e</t>
+          <t>576054f4a05b9713fb1ad346cae092659fa7df76d87c0f053e60e4018c5b6886</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">

--- a/output/第10期計画_中間報告の根拠対照表.xlsx
+++ b/output/第10期計画_中間報告の根拠対照表.xlsx
@@ -2955,7 +2955,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>e56026a6ce5d1a97a8995fbe9fdc91cf647bd8ab44ecf883b0464c8177e17814</t>
+          <t>bf7d2024516f90a8f9edf0a166a4c215f9ea2f1d5c5f7aceeab1ef19cfc49c99</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>be3ba1de4dbe12eaca9e04aa0021ac0ff722da7d6dae962af109ca073eab57ef</t>
+          <t>6a2f91a4f02a6edaf2a47fab3b5d0e0cdfd5146d85a62188cec45ca5f1417966</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>1a06b1c88498f4efbfb16b94840fdb2c33f92629c192fd892cfe81bb18af69e6</t>
+          <t>d3019d3caf0498fbad10da7d70f73be1a9b515c40d13af33c918b3784137aab6</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>f001d27820947b2fcb585c6151a47bf582c06c646d943a67efa70fdeb9931700</t>
+          <t>6ee2101a875cb71d13d9f955360c8ad3fa3d79f207366fad682803c6f13903da</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>1dbe19ecdb75809e98475461310d66a74f45bd671a96c709d141d2ed49d1b01c</t>
+          <t>3e4e757f367ed42fb27c232dba2c3efc0a3d06204b3dccaa30e92ced61af9164</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>ae55e00c0703490c41f3b0474066c123dff836bfb6dc1d98317b5bb715e272f1</t>
+          <t>b2f9b672fb3b4bcf697d43e4441a80f0cb861b9d9d4515658ae84b2bd8a86cf2</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>13d63efa203a9a7c1a085eb9d73ea9d6e565f2ffb6ae0329143b9458d9f47ca2</t>
+          <t>f99c87b5119b4bfc989bf9d0709cc2e36a8782faef12cc9bfd5c2ad58fae4108</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>68c3a6839d61dd3ae5af3f04fc980cd194b92a4e93f9c129b472a5277ef60a00</t>
+          <t>deef7fd45972b91d5c418904727639c767087b7a452457c2789d220da8dae19c</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>62d9f42159a69ea68d4adc24272bce03b9f9c5ca0704728a71787798622839d5</t>
+          <t>dca4667e4992a0c9c918e0053a27d49fc54c02e0ecbcde51e71884339b9c6418</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
